--- a/BA-Excel/Consumer-Regression.xlsx
+++ b/BA-Excel/Consumer-Regression.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Documents\DSBACODINGTEST\BA-Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99EAA4A-646B-48DF-8E8C-2BEDB8C4BB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79112C85-9D4E-4E6E-89FA-B051C83B968F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Income(in 1000's)</t>
   </si>
@@ -82,9 +82,6 @@
     <t>Beta2</t>
   </si>
   <si>
-    <t>Beta3</t>
-  </si>
-  <si>
     <t>yhat</t>
   </si>
   <si>
@@ -93,16 +90,38 @@
   <si>
     <t>sum of square errors</t>
   </si>
+  <si>
+    <t>Beta0</t>
+  </si>
+  <si>
+    <t>SSREGRESSION</t>
+  </si>
+  <si>
+    <t>SST</t>
+  </si>
+  <si>
+    <t>sum of squares regression</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.000000"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -146,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -169,25 +188,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -406,14 +441,16 @@
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="8" width="8.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -424,8 +461,8 @@
       <c r="B1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>5</v>
+      <c r="C1" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -439,7 +476,7 @@
         <v>1304.9066804107376</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2" s="7">
         <f>SUM(E4:E53)</f>
@@ -457,10 +494,16 @@
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>7</v>
+      <c r="F3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -481,6 +524,18 @@
         <f>(C4-D4)^2</f>
         <v>21601.543927826991</v>
       </c>
+      <c r="F4" s="10">
+        <f>(C4-$H$7)^2</f>
+        <v>2697.7636000000057</v>
+      </c>
+      <c r="G4" s="3">
+        <f>(D4-$H$7)^2</f>
+        <v>39567.032821700057</v>
+      </c>
+      <c r="I4">
+        <f>CORREL(B4:B53,C4:C53)</f>
+        <v>0.75284316530535922</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -500,6 +555,18 @@
         <f t="shared" ref="E5:E53" si="1">(C5-D5)^2</f>
         <v>21759.952246115525</v>
       </c>
+      <c r="F5" s="10">
+        <f t="shared" ref="F5:F53" si="2">(C5-$H$7)^2</f>
+        <v>648121.60359999991</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" ref="G5:G53" si="3">(D5-$H$7)^2</f>
+        <v>907394.46197133476</v>
+      </c>
+      <c r="I5">
+        <f>CORREL(C4:C53,A4:A53)</f>
+        <v>0.63097418573647401</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -519,6 +586,18 @@
         <f t="shared" si="1"/>
         <v>1715196.6419704603</v>
       </c>
+      <c r="F6" s="10">
+        <f t="shared" si="2"/>
+        <v>1290359.6836000001</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" si="3"/>
+        <v>30176.957325270872</v>
+      </c>
+      <c r="I6">
+        <f>CORREL(A4:A53,B4:B53)</f>
+        <v>0.17253349735092791</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -538,6 +617,18 @@
         <f t="shared" si="1"/>
         <v>1.0694815247268235</v>
       </c>
+      <c r="F7" s="10">
+        <f t="shared" si="2"/>
+        <v>605190.64360000007</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="3"/>
+        <v>606800.73789459362</v>
+      </c>
+      <c r="H7" s="3">
+        <f>AVERAGE(C4:C53)</f>
+        <v>3964.06</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -557,6 +648,14 @@
         <f t="shared" si="1"/>
         <v>1393864.5961470145</v>
       </c>
+      <c r="F8" s="10">
+        <f t="shared" si="2"/>
+        <v>4410252.0035999995</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="3"/>
+        <v>845369.12567476614</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -576,6 +675,21 @@
         <f t="shared" si="1"/>
         <v>52986.561887994736</v>
       </c>
+      <c r="F9" s="10">
+        <f t="shared" si="2"/>
+        <v>11223.283600000012</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="3"/>
+        <v>15437.590626940109</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="7">
+        <f>SUM(G4:G53)</f>
+        <v>35250707.245937474</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -595,6 +709,21 @@
         <f t="shared" si="1"/>
         <v>24374.259995084281</v>
       </c>
+      <c r="F10" s="10">
+        <f t="shared" si="2"/>
+        <v>1520436.9635999999</v>
+      </c>
+      <c r="G10" s="3">
+        <f t="shared" si="3"/>
+        <v>1159794.2065326022</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="7">
+        <f>J9+J2</f>
+        <v>42699100.393474355</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -614,6 +743,14 @@
         <f t="shared" si="1"/>
         <v>26.861106031333541</v>
       </c>
+      <c r="F11" s="10">
+        <f t="shared" si="2"/>
+        <v>379529.92359999992</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" si="3"/>
+        <v>385942.57941613073</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -633,6 +770,14 @@
         <f t="shared" si="1"/>
         <v>23368.040948489179</v>
       </c>
+      <c r="F12" s="10">
+        <f t="shared" si="2"/>
+        <v>639904.00360000005</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="3"/>
+        <v>907839.44187877094</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -652,6 +797,18 @@
         <f t="shared" si="1"/>
         <v>2155.2153315265614</v>
       </c>
+      <c r="F13" s="10">
+        <f t="shared" si="2"/>
+        <v>21298.483600000014</v>
+      </c>
+      <c r="G13" s="3">
+        <f t="shared" si="3"/>
+        <v>9903.3751873517449</v>
+      </c>
+      <c r="I13">
+        <f>J9/J10</f>
+        <v>0.82556088819437501</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -671,6 +828,18 @@
         <f t="shared" si="1"/>
         <v>1011798.0408007477</v>
       </c>
+      <c r="F14" s="10">
+        <f t="shared" si="2"/>
+        <v>59506.723600000027</v>
+      </c>
+      <c r="G14" s="3">
+        <f t="shared" si="3"/>
+        <v>580555.18935069581</v>
+      </c>
+      <c r="I14">
+        <f>1-J2/J10</f>
+        <v>0.8255608881943749</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -690,6 +859,14 @@
         <f t="shared" si="1"/>
         <v>10296.665308243222</v>
       </c>
+      <c r="F15" s="10">
+        <f t="shared" si="2"/>
+        <v>64994.403600000027</v>
+      </c>
+      <c r="G15" s="3">
+        <f t="shared" si="3"/>
+        <v>127029.85980165625</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -709,8 +886,20 @@
         <f t="shared" si="1"/>
         <v>6208.3054403123797</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F16" s="10">
+        <f t="shared" si="2"/>
+        <v>2211347.4435999999</v>
+      </c>
+      <c r="G16" s="3">
+        <f t="shared" si="3"/>
+        <v>1983216.5046571081</v>
+      </c>
+      <c r="I16">
+        <f>CORREL(C4:C53,D4:D53)</f>
+        <v>0.90860392142669955</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>33</v>
       </c>
@@ -728,8 +917,20 @@
         <f t="shared" si="1"/>
         <v>356273.35582169099</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F17" s="10">
+        <f t="shared" si="2"/>
+        <v>2102674.0035999999</v>
+      </c>
+      <c r="G17" s="3">
+        <f t="shared" si="3"/>
+        <v>727905.21844233002</v>
+      </c>
+      <c r="I17">
+        <f>I16^2</f>
+        <v>0.82556108603197598</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>65</v>
       </c>
@@ -747,8 +948,16 @@
         <f t="shared" si="1"/>
         <v>98243.000144070247</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F18" s="10">
+        <f t="shared" si="2"/>
+        <v>62470.003600000025</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" si="3"/>
+        <v>317394.08840555546</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>63</v>
       </c>
@@ -766,8 +975,16 @@
         <f t="shared" si="1"/>
         <v>21765.940505551105</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F19" s="10">
+        <f t="shared" si="2"/>
+        <v>1001880.8836000001</v>
+      </c>
+      <c r="G19" s="3">
+        <f t="shared" si="3"/>
+        <v>728303.7713273518</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>42</v>
       </c>
@@ -785,8 +1002,16 @@
         <f t="shared" si="1"/>
         <v>178308.61696721765</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="10">
+        <f t="shared" si="2"/>
+        <v>200650.24360000005</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="3"/>
+        <v>757258.56942489755</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>21</v>
       </c>
@@ -804,8 +1029,16 @@
         <f t="shared" si="1"/>
         <v>70379.128521088511</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="10">
+        <f t="shared" si="2"/>
+        <v>2298437.9235999999</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" si="3"/>
+        <v>1564423.9690509064</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>44</v>
       </c>
@@ -823,8 +1056,16 @@
         <f t="shared" si="1"/>
         <v>15389.252395255384</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="10">
+        <f t="shared" si="2"/>
+        <v>939077.28359999985</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" si="3"/>
+        <v>714036.11083262146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>37</v>
       </c>
@@ -842,8 +1083,16 @@
         <f t="shared" si="1"/>
         <v>19967.228576061047</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F23" s="10">
+        <f t="shared" si="2"/>
+        <v>42824.163600000022</v>
+      </c>
+      <c r="G23" s="3">
+        <f t="shared" si="3"/>
+        <v>121274.88944425917</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>62</v>
       </c>
@@ -861,8 +1110,16 @@
         <f t="shared" si="1"/>
         <v>32787.935197626197</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F24" s="10">
+        <f t="shared" si="2"/>
+        <v>2937590.3236000002</v>
+      </c>
+      <c r="G24" s="3">
+        <f t="shared" si="3"/>
+        <v>2349676.9742255043</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -880,8 +1137,16 @@
         <f t="shared" si="1"/>
         <v>306266.65118668735</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F25" s="10">
+        <f t="shared" si="2"/>
+        <v>116321.92359999997</v>
+      </c>
+      <c r="G25" s="3">
+        <f t="shared" si="3"/>
+        <v>800083.08335901436</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>55</v>
       </c>
@@ -899,8 +1164,16 @@
         <f t="shared" si="1"/>
         <v>102585.99105443367</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F26" s="10">
+        <f t="shared" si="2"/>
+        <v>1787408.5636000002</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" si="3"/>
+        <v>2746412.8611287591</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>42</v>
       </c>
@@ -918,8 +1191,16 @@
         <f t="shared" si="1"/>
         <v>151385.72543841568</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F27" s="10">
+        <f t="shared" si="2"/>
+        <v>891249.28359999985</v>
+      </c>
+      <c r="G27" s="3">
+        <f t="shared" si="3"/>
+        <v>307999.2643478805</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>41</v>
       </c>
@@ -937,8 +1218,16 @@
         <f t="shared" si="1"/>
         <v>108523.32643166113</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F28" s="10">
+        <f t="shared" si="2"/>
+        <v>746392.32360000012</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" si="3"/>
+        <v>1424129.0644207771</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>54</v>
       </c>
@@ -956,8 +1245,16 @@
         <f t="shared" si="1"/>
         <v>116375.28160290801</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F29" s="10">
+        <f t="shared" si="2"/>
+        <v>2588687.9236000003</v>
+      </c>
+      <c r="G29" s="3">
+        <f t="shared" si="3"/>
+        <v>1607321.3665340939</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>30</v>
       </c>
@@ -975,8 +1272,16 @@
         <f t="shared" si="1"/>
         <v>5211.6465287762676</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F30" s="10">
+        <f t="shared" si="2"/>
+        <v>1907326.7235999999</v>
+      </c>
+      <c r="G30" s="3">
+        <f t="shared" si="3"/>
+        <v>1713136.1364573136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>48</v>
       </c>
@@ -994,8 +1299,16 @@
         <f t="shared" si="1"/>
         <v>66625.390613916883</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F31" s="10">
+        <f t="shared" si="2"/>
+        <v>9615.7635999999893</v>
+      </c>
+      <c r="G31" s="3">
+        <f t="shared" si="3"/>
+        <v>126863.44202871573</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>34</v>
       </c>
@@ -1013,8 +1326,16 @@
         <f t="shared" si="1"/>
         <v>393011.77284771425</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F32" s="10">
+        <f t="shared" si="2"/>
+        <v>142929.36359999995</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" si="3"/>
+        <v>61924.585764379779</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>67</v>
       </c>
@@ -1032,8 +1353,16 @@
         <f t="shared" si="1"/>
         <v>7569.1624782145436</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F33" s="10">
+        <f t="shared" si="2"/>
+        <v>1151200.2436000002</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" si="3"/>
+        <v>972075.84230304253</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>50</v>
       </c>
@@ -1051,8 +1380,16 @@
         <f t="shared" si="1"/>
         <v>4781.3088853784402</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F34" s="10">
+        <f t="shared" si="2"/>
+        <v>128924.08359999995</v>
+      </c>
+      <c r="G34" s="3">
+        <f t="shared" si="3"/>
+        <v>84049.542217521637</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>67</v>
       </c>
@@ -1070,8 +1407,16 @@
         <f t="shared" si="1"/>
         <v>1498.0938788692142</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F35" s="10">
+        <f t="shared" si="2"/>
+        <v>1906995.2836000002</v>
+      </c>
+      <c r="G35" s="3">
+        <f t="shared" si="3"/>
+        <v>1801594.2107581953</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>55</v>
       </c>
@@ -1089,8 +1434,16 @@
         <f t="shared" si="1"/>
         <v>11026.099771099087</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F36" s="10">
+        <f t="shared" si="2"/>
+        <v>1976667.2836000002</v>
+      </c>
+      <c r="G36" s="3">
+        <f t="shared" si="3"/>
+        <v>1692431.2579080388</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>52</v>
       </c>
@@ -1108,8 +1461,16 @@
         <f t="shared" si="1"/>
         <v>22376.281010862138</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F37" s="10">
+        <f t="shared" si="2"/>
+        <v>5484.8835999999919</v>
+      </c>
+      <c r="G37" s="3">
+        <f t="shared" si="3"/>
+        <v>50017.996220590896</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>62</v>
       </c>
@@ -1127,8 +1488,16 @@
         <f t="shared" si="1"/>
         <v>76707.69436484795</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F38" s="10">
+        <f t="shared" si="2"/>
+        <v>548992.08360000013</v>
+      </c>
+      <c r="G38" s="3">
+        <f t="shared" si="3"/>
+        <v>215276.011803531</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>64</v>
       </c>
@@ -1146,8 +1515,16 @@
         <f t="shared" si="1"/>
         <v>360.66946402342506</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F39" s="10">
+        <f t="shared" si="2"/>
+        <v>37225.843600000022</v>
+      </c>
+      <c r="G39" s="3">
+        <f t="shared" si="3"/>
+        <v>30258.150338548716</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>22</v>
       </c>
@@ -1165,8 +1542,16 @@
         <f t="shared" si="1"/>
         <v>226843.26410815507</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F40" s="10">
+        <f t="shared" si="2"/>
+        <v>148271.20359999995</v>
+      </c>
+      <c r="G40" s="3">
+        <f t="shared" si="3"/>
+        <v>741907.72717658535</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>29</v>
       </c>
@@ -1184,8 +1569,16 @@
         <f t="shared" si="1"/>
         <v>39622.532845527458</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F41" s="10">
+        <f t="shared" si="2"/>
+        <v>5484.8835999999919</v>
+      </c>
+      <c r="G41" s="3">
+        <f t="shared" si="3"/>
+        <v>74591.309037578088</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>39</v>
       </c>
@@ -1203,8 +1596,16 @@
         <f t="shared" si="1"/>
         <v>114030.65401781397</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F42" s="10">
+        <f t="shared" si="2"/>
+        <v>984183.04359999986</v>
+      </c>
+      <c r="G42" s="3">
+        <f t="shared" si="3"/>
+        <v>428207.61963060423</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>35</v>
       </c>
@@ -1222,8 +1623,16 @@
         <f t="shared" si="1"/>
         <v>90086.046059844695</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F43" s="10">
+        <f t="shared" si="2"/>
+        <v>710750.16359999985</v>
+      </c>
+      <c r="G43" s="3">
+        <f t="shared" si="3"/>
+        <v>1306913.9585289753</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>39</v>
       </c>
@@ -1241,8 +1650,16 @@
         <f t="shared" si="1"/>
         <v>25832.305732204786</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F44" s="10">
+        <f t="shared" si="2"/>
+        <v>47934.723600000027</v>
+      </c>
+      <c r="G44" s="3">
+        <f t="shared" si="3"/>
+        <v>3389.0658713619646</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>54</v>
       </c>
@@ -1260,8 +1677,16 @@
         <f t="shared" si="1"/>
         <v>187467.03630456343</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F45" s="10">
+        <f t="shared" si="2"/>
+        <v>54784.083599999976</v>
+      </c>
+      <c r="G45" s="3">
+        <f t="shared" si="3"/>
+        <v>39567.032821700057</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>23</v>
       </c>
@@ -1279,8 +1704,16 @@
         <f t="shared" si="1"/>
         <v>6043.4250767026369</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F46" s="10">
+        <f t="shared" si="2"/>
+        <v>26549.443600000017</v>
+      </c>
+      <c r="G46" s="3">
+        <f t="shared" si="3"/>
+        <v>57926.606910507981</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>27</v>
       </c>
@@ -1298,8 +1731,16 @@
         <f t="shared" si="1"/>
         <v>79.414533810133051</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F47" s="10">
+        <f t="shared" si="2"/>
+        <v>1087974.1635999999</v>
+      </c>
+      <c r="G47" s="3">
+        <f t="shared" si="3"/>
+        <v>1106644.0015824314</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>26</v>
       </c>
@@ -1317,8 +1758,16 @@
         <f t="shared" si="1"/>
         <v>3298.6780358929946</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F48" s="10">
+        <f t="shared" si="2"/>
+        <v>408244.32360000006</v>
+      </c>
+      <c r="G48" s="3">
+        <f t="shared" si="3"/>
+        <v>484936.91374138888</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>61</v>
       </c>
@@ -1336,8 +1785,16 @@
         <f t="shared" si="1"/>
         <v>54938.781557938186</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F49" s="10">
+        <f t="shared" si="2"/>
+        <v>95443.923600000038</v>
+      </c>
+      <c r="G49" s="3">
+        <f t="shared" si="3"/>
+        <v>5557.6676859189974</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>30</v>
       </c>
@@ -1355,8 +1812,16 @@
         <f t="shared" si="1"/>
         <v>3081.6431467686675</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F50" s="10">
+        <f t="shared" si="2"/>
+        <v>804716.64359999995</v>
+      </c>
+      <c r="G50" s="3">
+        <f t="shared" si="3"/>
+        <v>907394.46197133476</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>22</v>
       </c>
@@ -1374,8 +1839,16 @@
         <f t="shared" si="1"/>
         <v>148236.59580054265</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F51" s="10">
+        <f t="shared" si="2"/>
+        <v>792206.80359999987</v>
+      </c>
+      <c r="G51" s="3">
+        <f t="shared" si="3"/>
+        <v>255070.39224110366</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46</v>
       </c>
@@ -1393,8 +1866,16 @@
         <f t="shared" si="1"/>
         <v>43889.309072688266</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F52" s="10">
+        <f t="shared" si="2"/>
+        <v>732633.28360000008</v>
+      </c>
+      <c r="G52" s="3">
+        <f t="shared" si="3"/>
+        <v>417887.57697645784</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>66</v>
       </c>
@@ -1412,18 +1893,26 @@
         <f t="shared" si="1"/>
         <v>53886.152966692491</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="F53" s="10">
+        <f t="shared" si="2"/>
+        <v>1404082.8036000002</v>
+      </c>
+      <c r="G53" s="3">
+        <f t="shared" si="3"/>
+        <v>907839.44187877094</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2361,7 +2850,7 @@
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/BA-Excel/Consumer-Regression.xlsx
+++ b/BA-Excel/Consumer-Regression.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Documents\DSBACODINGTEST\BA-Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79112C85-9D4E-4E6E-89FA-B051C83B968F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCFEEDB-A3E7-48B8-B27F-05E4379CE19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
